--- a/Zinc/4. Exploratory data analysis/Inherent_characteristics_summary.xlsx
+++ b/Zinc/4. Exploratory data analysis/Inherent_characteristics_summary.xlsx
@@ -1,32 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/4. Exploratory data analysis/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_1D57C5568060CB5E4B3A6CCDEE8AEFFA6AB2A627" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0CCD83E-D43F-42AB-9C9F-5C5BFE7B5095}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sites by type" sheetId="4" r:id="rId1"/>
-    <sheet name="Sites by regime" sheetId="5" r:id="rId2"/>
-    <sheet name="Sites by development" sheetId="6" r:id="rId3"/>
-    <sheet name="Sites retained" sheetId="8" r:id="rId4"/>
+    <sheet name="Sites by type" sheetId="17" state="visible" r:id="rId1"/>
+    <sheet name="Sites by regime" sheetId="18" state="visible" r:id="rId2"/>
+    <sheet name="Sites by development" sheetId="19" state="visible" r:id="rId3"/>
+    <sheet name="Sites retained" sheetId="20" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sites retained'!$A$1:$B$1</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>Type</t>
   </si>
@@ -224,13 +214,212 @@
   </si>
   <si>
     <t>BSL6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_Sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tributaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonPerennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK13.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK16.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downtown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK23.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK18.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mill Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S_TRIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK11.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK10.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gum Hollow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinhook Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK7.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCK0.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -556,506 +745,501 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
+        <v>68</v>
+      </c>
+      <c r="B2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
+        <v>69</v>
+      </c>
+      <c r="B3" t="n">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
+        <v>71</v>
+      </c>
+      <c r="B2" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
+        <v>72</v>
+      </c>
+      <c r="B3" t="n">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
+        <v>74</v>
+      </c>
+      <c r="B2" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
+        <v>75</v>
+      </c>
+      <c r="B3" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
+        <v>76</v>
+      </c>
+      <c r="B4" t="n">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{00000000-0001-0000-0400-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B47">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Zinc/4. Exploratory data analysis/Inherent_characteristics_summary.xlsx
+++ b/Zinc/4. Exploratory data analysis/Inherent_characteristics_summary.xlsx
@@ -6,10 +6,10 @@
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sites by type" sheetId="17" state="visible" r:id="rId1"/>
-    <sheet name="Sites by regime" sheetId="18" state="visible" r:id="rId2"/>
-    <sheet name="Sites by development" sheetId="19" state="visible" r:id="rId3"/>
-    <sheet name="Sites retained" sheetId="20" state="visible" r:id="rId4"/>
+    <sheet name="Sites by type" sheetId="21" state="visible" r:id="rId1"/>
+    <sheet name="Sites by regime" sheetId="22" state="visible" r:id="rId2"/>
+    <sheet name="Sites by development" sheetId="23" state="visible" r:id="rId3"/>
+    <sheet name="Sites retained" sheetId="24" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
